--- a/entrepreneur_forms/004_join_the_wealth_building_group--entrepreneur_forms.xlsx
+++ b/entrepreneur_forms/004_join_the_wealth_building_group--entrepreneur_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Member Details Email</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Member Details Phone</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>consent</t>
+          <t>Consent Consent</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -868,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>I agree</t>
         </is>
       </c>
     </row>
@@ -918,46 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>i_do_not_agree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>consent_consent_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>consent_consent_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Option 4</t>
+          <t>I do not agree</t>
         </is>
       </c>
     </row>
